--- a/output/pdf_financials_xlsx/QBAT.xlsx
+++ b/output/pdf_financials_xlsx/QBAT.xlsx
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.898041</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.929541</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.001844</v>
       </c>
     </row>
     <row r="93">
@@ -3037,7 +3037,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>3.898041</v>
       </c>

--- a/output/pdf_financials_xlsx/QBAT.xlsx
+++ b/output/pdf_financials_xlsx/QBAT.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000976</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.053715</v>
+        <v>-1.054691</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.112053</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.053715</v>
+        <v>-1.054691</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.112053</v>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.165073</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.210865</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000368</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.165073</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.210865</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000368</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.198773</v>
+        <v>0.0337</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.229171</v>
+        <v>0.018306</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000722</v>
+        <v>0.000354</v>
       </c>
     </row>
     <row r="49">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">

--- a/output/pdf_financials_xlsx/QBAT.xlsx
+++ b/output/pdf_financials_xlsx/QBAT.xlsx
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.004184</v>
+        <v>-0.004184</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.003434</v>
+        <v>-0.003434</v>
       </c>
     </row>
     <row r="18">
@@ -3339,7 +3339,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>-0.004184</v>
       </c>
@@ -3579,7 +3583,11 @@
           <t>Proceeds from shares issued for cash</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.5</v>
       </c>
@@ -4197,7 +4205,11 @@
           <t>Fair value of warrants issued for non-brokered private placement $</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.212995</v>
       </c>
@@ -4652,7 +4664,11 @@
           <t>Deferred income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.004184</v>
       </c>
